--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>ashok kumar bomjon</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851177886</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851177886</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9851177886</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9851177886</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.72007</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.72007</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1176,25 +1170,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.3763</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.3763</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no signal showing   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -671,27 +718,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,13 +774,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -723,17 +792,17 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -746,18 +815,18 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1215,6 +1284,214 @@
       <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377973</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Bibek ghemasu</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9861518467</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861518467</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:52:34 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:34:13 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinyak , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9861518467@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>02:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,14 +546,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -634,10 +652,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -657,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -722,45 +746,73 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2</v>
+      <c r="E5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -785,12 +837,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1354,10 +1406,8 @@
           <t>Bibek ghemasu</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9861518467</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9861518467</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1447,10 +1497,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1461,37 +1509,469 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377918</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Idea Hub</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9851160975</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 11:13:48 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.68498</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>near Holy Vision Technical Campus, M8MM+WV7, Sankhamul Marg, Kathmandu 44600, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ideahub@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>02:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB154</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.33462</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 41m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 45m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>iptv isuue</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378266</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise sound service Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9851005949</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851005949</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 05:00:32 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:55:34 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.74037</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Vidhyalaya (???????? ????????) - School Budhanilkantha 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>rajzcrestha99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L2-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.36019</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>19h 55m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1610,10 +1610,8 @@
           <t>Idea Hub</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851160975</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851160975</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1648,10 +1646,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.68498</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.68498</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1707,25 +1703,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB154</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33462</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33462</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1826,10 +1818,8 @@
           <t>Sunrise sound service Pvt Ltd</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9851005949</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9851005949</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1864,10 +1854,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.74037</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.74037</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1923,25 +1911,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L2-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.36019</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.36019</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv isuue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,14 +546,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -580,18 +580,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -675,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,15 +744,20 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -749,13 +773,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>2</v>
+      <c r="F2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -768,12 +795,15 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -787,12 +817,15 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -806,13 +839,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>4</v>
+      <c r="F5" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -866,13 +902,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1959,6 +1995,210 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 2:38 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371692</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Pralad Upreti</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Pralad Upreti</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9855089977</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9846588576</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 12:34:10 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:38:42 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>near by Universal Dental Hospital - Dental hygienist - Kathmandu Metropolitan, Kathmandu, Bagmati, N</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>20:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>11d 2h 4m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -908,7 +908,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2062,10 +2062,8 @@
           <t>Pralad Upreti</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9855089977</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9855089977</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2151,10 +2149,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2165,7 +2161,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -845,10 +845,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -908,10 +908,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2195,6 +2195,218 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378099</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9861778881</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9861778881K</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:54:01 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.65445</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Sitapakha, Imadol, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>crackmaharjan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.3385</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -908,7 +908,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2252,20 +2252,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9861778881</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9861778881</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2300,10 +2294,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.65445</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.65445</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2355,25 +2347,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.3385</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.3385</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -582,36 +582,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>83.3%</t>
+      <c r="B7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -626,10 +644,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -666,14 +684,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>IPTV Issue</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -682,28 +700,51 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
@@ -720,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -754,10 +796,15 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -779,10 +826,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -803,7 +853,10 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -825,30 +878,61 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>6</v>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -896,7 +980,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -908,12 +992,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -2395,6 +2479,646 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>STB return</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373194</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Lamichhane</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851239211</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851239211</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 07:29:56 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:59:10 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71923</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati near New Generation Driving School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>saugatlamichanne165@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>05:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L61-4</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.37675</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 29m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:05 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378747</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Ekata Interprises</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9849875913</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9849875913</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 09:16:00 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:05:07 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>haribot chowk hattiban, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>digambar.das27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>07:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L7-2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>7h 49m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378099</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Krasan Maharjan</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9861778881</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9861778881K</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 02:16:55 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:33:38 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.65445</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Sitapakha, Imadol, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>crackmaharjan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.3385</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -829,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -873,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -911,28 +911,53 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>8</v>
+      <c r="F7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -964,7 +989,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -974,7 +999,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -2536,20 +2561,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Saugat Lamichhane</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851239211</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851239211</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2584,10 +2603,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71923</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71923</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2643,25 +2660,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L61-4</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.37675</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.37675</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : STB return  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2762,10 +2775,8 @@
           <t>Ekata Interprises</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9849875913</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9849875913</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2855,10 +2866,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2869,7 +2878,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2960,20 +2969,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Krasan Maharjan</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9861778881</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9861778881</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3008,10 +3011,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.65445</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.65445</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -3067,53 +3068,469 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.3385</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.3385</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 16m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 16m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:12 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379083</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:18:42 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:18:42 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:12:58 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.65241</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Imadol Ochu Height surayada school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>frankwankey@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L33-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.34204</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378866</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:14:05 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:12:24 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:10:59 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.66608</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near to Boje Pokhari - Pond Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35222</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -761,10 +761,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -863,14 +863,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -936,28 +936,53 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>10</v>
+      <c r="G8" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1006,7 +1031,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3183,10 +3208,8 @@
           <t>Sujan Dulal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9849715976</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9849715976</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3221,10 +3244,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.65241</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.65241</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3276,25 +3297,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L33-8</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.34204</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.34204</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3395,10 +3412,8 @@
           <t>Padam Nepali</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860495460</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860495460</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3433,10 +3448,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.66608</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.66608</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3484,47 +3497,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35222</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35222</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>6h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>6h 56m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>6h 58m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -3533,6 +3542,214 @@
       <c r="AX12" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378708</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Raju subedi</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Raju subedi</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9843663665</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>KLK9843663665</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 08:38:49 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:35:32 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Tahachal near, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>9843663665@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>07:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>8h 56m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Oct_2026.xlsx
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3612,10 +3612,8 @@
           <t>Raju subedi</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9843663665</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9843663665</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3705,10 +3703,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3719,7 +3715,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
